--- a/notes/meetings/meeting-20260409/凤御美业八大会员权益.xlsx
+++ b/notes/meetings/meeting-20260409/凤御美业八大会员权益.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9060"/>
+    <workbookView windowWidth="29100" windowHeight="13360"/>
   </bookViews>
   <sheets>
     <sheet name="凤御会员权益" sheetId="7" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="69">
   <si>
     <t>凤御美业八大会员权益</t>
   </si>
@@ -48,9 +48,6 @@
     <t>生日礼</t>
   </si>
   <si>
-    <t>定制礼</t>
-  </si>
-  <si>
     <t>感恩日（爱你）</t>
   </si>
   <si>
@@ -66,16 +63,7 @@
     <t>周年纪念日</t>
   </si>
   <si>
-    <t>凤御用户</t>
-  </si>
-  <si>
-    <t>＜1990</t>
-  </si>
-  <si>
-    <t>/</t>
-  </si>
-  <si>
-    <t>初钻·会员</t>
+    <t>会员</t>
   </si>
   <si>
     <t>1990-9999元</t>
@@ -106,7 +94,7 @@
     <t>送价值300元家居现金券或一个招牌项目</t>
   </si>
   <si>
-    <t>星钻·贵宾</t>
+    <t>星钻</t>
   </si>
   <si>
     <t>10000-29999元</t>
@@ -122,7 +110,7 @@
     <t>送价值500元家居现金券或一个招牌项目</t>
   </si>
   <si>
-    <t>粉钻·铁粉</t>
+    <t>粉钻</t>
   </si>
   <si>
     <t>30000-59999元</t>
@@ -131,114 +119,36 @@
     <t>定制王牌任选2次+家居单品券600元</t>
   </si>
   <si>
+    <t>1、价值1280元明星项目体验券
+2、当月家居产品/项目折扣9折</t>
+  </si>
+  <si>
+    <t>送价值500元家居现金券或一个王牌项目</t>
+  </si>
+  <si>
+    <t>金钻</t>
+  </si>
+  <si>
+    <t>60000-99999元</t>
+  </si>
+  <si>
+    <t>尊享明星项目单部位3次+家居单品券1500元</t>
+  </si>
+  <si>
+    <t>1、价值1980元明星项目体验券
+2、当月家居产品/项目折扣8.8折</t>
+  </si>
+  <si>
+    <t>送价值1000元家居现金券或一个明星项目</t>
+  </si>
+  <si>
+    <t>黑钻</t>
+  </si>
+  <si>
+    <t>10w+</t>
+  </si>
+  <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">1、价值1280元明星项目体验券
-2、当月家居产品/项目折扣9折
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t>3、生日专属土鸡+</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t>蛋糕/鲜花</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t>1、</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t>专属床上用品</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t>+定制水杯+精美茶歇
-3、一年四节礼物
-（三八、端午、中秋、春节）</t>
-    </r>
-  </si>
-  <si>
-    <t>送价值500元家居现金券或一个王牌项目</t>
-  </si>
-  <si>
-    <t>金钻·女神</t>
-  </si>
-  <si>
-    <t>60000-99999元</t>
-  </si>
-  <si>
-    <t>尊享明星项目单部位3次+家居单品券1500元</t>
-  </si>
-  <si>
-    <t>1、价值1980元明星项目体验券
-2、当月家居产品/项目折扣8.8折
-3、生日专属土鸡+蛋糕/鲜花</t>
-  </si>
-  <si>
-    <t>1、专属床上用品+定制水杯+拖鞋+毛巾+精美茶歇
-2、一年四节礼物
-（三八、端午、中秋、春节）
-3、新品优先免费感受项目</t>
-  </si>
-  <si>
-    <t>送价值1000元家居现金券或一个明星项目</t>
-  </si>
-  <si>
-    <t>黑钻·女王</t>
-  </si>
-  <si>
-    <t>10w+</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
       <t>定制明星美肤项目任选3次+</t>
     </r>
     <r>
@@ -254,19 +164,19 @@
   </si>
   <si>
     <t>1、价值2980元明星项目体验券
-2、当月家居产品/项目折扣8.5折
-3、生日专属土鸡+蛋糕+鲜花</t>
+2、当月家居产品/项目折扣8.5折</t>
   </si>
   <si>
     <t>规则</t>
   </si>
   <si>
+    <t>/</t>
+  </si>
+  <si>
     <t>当月20号-月底，仅限兑换指定主推品</t>
   </si>
   <si>
-    <t>1.代金券新老客各15%，按单次会员价兑换所有项目；
-2.同一个新客最多请客2次；
-3.新客福利不可与门店其他福利同时享受（按最优选择）</t>
+    <t>代金券新老客各15%，按单次会员价兑换所有项目；</t>
   </si>
   <si>
     <t>成为凤御会员当天，定为会员周年纪念日；现金券恕不找零，但可补差价。</t>
@@ -338,6 +248,9 @@
   </si>
   <si>
     <t>费用</t>
+  </si>
+  <si>
+    <t>粉钻·铁粉</t>
   </si>
   <si>
     <r>
@@ -392,6 +305,9 @@
       <t xml:space="preserve">
 （三八、端午、中秋、春节）</t>
     </r>
+  </si>
+  <si>
+    <t>金钻·女神</t>
   </si>
   <si>
     <r>
@@ -449,6 +365,9 @@
     </r>
   </si>
   <si>
+    <t>黑钻·女王</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -504,7 +423,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -563,13 +482,6 @@
     </font>
     <font>
       <b/>
-      <sz val="16"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <sz val="14"/>
       <color indexed="8"/>
       <name val="微软雅黑"/>
@@ -596,10 +508,17 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -607,14 +526,14 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -622,7 +541,7 @@
       <b/>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -630,7 +549,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -638,7 +557,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -646,7 +565,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -654,14 +573,14 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -669,7 +588,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -677,7 +596,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -685,14 +604,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -700,42 +619,42 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -762,6 +681,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor indexed="13"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.15"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -769,18 +700,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-0.1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="13"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1001,32 +920,6 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
         <color auto="1"/>
       </right>
@@ -1063,6 +956,32 @@
       </top>
       <bottom style="thin">
         <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1359,7 +1278,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1369,35 +1288,35 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1426,43 +1345,40 @@
     <xf numFmtId="49" fontId="7" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1471,63 +1387,57 @@
     <xf numFmtId="49" fontId="2" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1788,25 +1698,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultColWidth="16.3333333333333" defaultRowHeight="19.9" customHeight="1"/>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr defaultColWidth="16.3359375" defaultRowHeight="19.9" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="15.2222222222222" style="13" customWidth="1"/>
+    <col min="1" max="1" width="15.21875" style="13" customWidth="1"/>
     <col min="2" max="2" width="29" style="13" customWidth="1"/>
-    <col min="3" max="3" width="46.462962962963" style="13" customWidth="1"/>
-    <col min="4" max="4" width="50.4444444444444" style="13" customWidth="1"/>
-    <col min="5" max="5" width="55.1111111111111" style="13" customWidth="1"/>
-    <col min="6" max="6" width="40.3981481481481" style="13" customWidth="1"/>
-    <col min="7" max="7" width="35.3518518518519" style="13" customWidth="1"/>
-    <col min="8" max="8" width="33.2222222222222" style="13" customWidth="1"/>
-    <col min="9" max="9" width="32.8888888888889" style="13" customWidth="1"/>
-    <col min="10" max="10" width="36.7685185185185" style="13" customWidth="1"/>
-    <col min="11" max="16381" width="16.3518518518519" style="13" customWidth="1"/>
-    <col min="16382" max="16382" width="16.3518518518519" style="13"/>
-    <col min="16383" max="16384" width="16.3333333333333" style="13"/>
+    <col min="3" max="3" width="46.4609375" style="13" customWidth="1"/>
+    <col min="4" max="4" width="50.4453125" style="13" customWidth="1"/>
+    <col min="5" max="5" width="40.3984375" style="13" customWidth="1"/>
+    <col min="6" max="6" width="35.3515625" style="13" customWidth="1"/>
+    <col min="7" max="7" width="33.21875" style="13" customWidth="1"/>
+    <col min="8" max="8" width="32.890625" style="13" customWidth="1"/>
+    <col min="9" max="9" width="36.765625" style="13" customWidth="1"/>
+    <col min="10" max="16380" width="16.3515625" style="13" customWidth="1"/>
+    <col min="16381" max="16381" width="16.3515625" style="13"/>
+    <col min="16382" max="16384" width="16.3359375" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" s="13" customFormat="1" ht="49" customHeight="1" spans="1:10">
+    <row r="1" s="13" customFormat="1" ht="49" customHeight="1" spans="1:9">
       <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
@@ -1818,9 +1727,8 @@
       <c r="G1" s="18"/>
       <c r="H1" s="18"/>
       <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
     </row>
-    <row r="2" s="14" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="2" s="14" customFormat="1" ht="25" customHeight="1" spans="1:9">
       <c r="A2" s="19" t="s">
         <v>1</v>
       </c>
@@ -1836,9 +1744,8 @@
       <c r="G2" s="19"/>
       <c r="H2" s="19"/>
       <c r="I2" s="19"/>
-      <c r="J2" s="19"/>
     </row>
-    <row r="3" s="14" customFormat="1" ht="25" customHeight="1" spans="1:10">
+    <row r="3" s="14" customFormat="1" ht="25" customHeight="1" spans="1:9">
       <c r="A3" s="20"/>
       <c r="B3" s="20"/>
       <c r="C3" s="21" t="s">
@@ -1847,268 +1754,214 @@
       <c r="D3" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="E3" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="22" t="s">
+      <c r="F3" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="21" t="s">
+      <c r="G3" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="22" t="s">
+      <c r="H3" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="22" t="s">
+      <c r="I3" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="21" t="s">
+    </row>
+    <row r="4" s="15" customFormat="1" ht="121" customHeight="1" spans="1:9">
+      <c r="A4" s="5" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" s="14" customFormat="1" ht="49" customHeight="1" spans="1:10">
-      <c r="A4" s="11" t="s">
+      <c r="B4" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="23" t="s">
+      <c r="C4" s="23" t="s">
         <v>13</v>
-      </c>
-      <c r="C4" s="24" t="s">
-        <v>14</v>
       </c>
       <c r="D4" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="J4" s="24" t="s">
-        <v>14</v>
+      <c r="E4" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" s="23" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="5" s="15" customFormat="1" ht="121" customHeight="1" spans="1:10">
-      <c r="A5" s="11" t="s">
+    <row r="5" s="15" customFormat="1" ht="93" customHeight="1" spans="1:9">
+      <c r="A5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="25" t="s">
+      <c r="F5" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="26" t="s">
+      <c r="G5" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="27" t="s">
+      <c r="H5" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="G5" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="I5" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="J5" s="26" t="s">
-        <v>23</v>
+      <c r="I5" s="23" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="6" s="15" customFormat="1" ht="93" customHeight="1" spans="1:10">
-      <c r="A6" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="25" t="s">
+    <row r="6" s="15" customFormat="1" ht="122" customHeight="1" spans="1:9">
+      <c r="A6" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="B6" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="26" t="s">
+      <c r="C6" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="G6" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="H6" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="I6" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="J6" s="26" t="s">
+      <c r="D6" s="23" t="s">
         <v>28</v>
       </c>
+      <c r="E6" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="I6" s="23" t="s">
+        <v>29</v>
+      </c>
     </row>
-    <row r="7" s="15" customFormat="1" ht="122" customHeight="1" spans="1:10">
-      <c r="A7" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" s="25" t="s">
+    <row r="7" s="15" customFormat="1" ht="137" customHeight="1" spans="1:9">
+      <c r="A7" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="B7" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="26" t="s">
+      <c r="C7" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="29" t="s">
+      <c r="D7" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="F7" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="G7" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="H7" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="I7" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="J7" s="26" t="s">
+      <c r="E7" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="I7" s="23" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="8" s="15" customFormat="1" ht="137" customHeight="1" spans="1:10">
-      <c r="A8" s="11" t="s">
+    <row r="8" s="15" customFormat="1" ht="131" customHeight="1" spans="1:9">
+      <c r="A8" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="26" t="s">
+      <c r="D8" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="E8" s="29" t="s">
+      <c r="E8" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" s="23" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" s="16" customFormat="1" ht="126" customHeight="1" spans="1:9">
+      <c r="A9" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="F8" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="G8" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="H8" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="I8" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="J8" s="26" t="s">
+      <c r="B9" s="27" t="s">
         <v>40</v>
       </c>
+      <c r="C9" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" s="33" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" s="33" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" s="34" t="s">
+        <v>40</v>
+      </c>
+      <c r="H9" s="34" t="s">
+        <v>40</v>
+      </c>
+      <c r="I9" s="35" t="s">
+        <v>43</v>
+      </c>
     </row>
-    <row r="9" s="15" customFormat="1" ht="131" customHeight="1" spans="1:10">
-      <c r="A9" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="B9" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="C9" s="28" t="s">
-        <v>43</v>
-      </c>
-      <c r="D9" s="26" t="s">
+    <row r="10" s="17" customFormat="1" ht="305" customHeight="1" spans="1:9">
+      <c r="A10" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="E9" s="29" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="G9" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="H9" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="I9" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="J9" s="26" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" s="16" customFormat="1" ht="126" customHeight="1" spans="1:10">
-      <c r="A10" s="30" t="s">
-        <v>45</v>
-      </c>
-      <c r="B10" s="31" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" s="33" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="31" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" s="34" t="s">
-        <v>46</v>
-      </c>
-      <c r="G10" s="34" t="s">
-        <v>47</v>
-      </c>
-      <c r="H10" s="35" t="s">
-        <v>14</v>
-      </c>
-      <c r="I10" s="35" t="s">
-        <v>14</v>
-      </c>
-      <c r="J10" s="36" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" s="17" customFormat="1" ht="305" customHeight="1" spans="1:10">
-      <c r="A11" s="37" t="s">
-        <v>49</v>
-      </c>
-      <c r="B11" s="37"/>
-      <c r="C11" s="37"/>
-      <c r="D11" s="38"/>
-      <c r="E11" s="37"/>
-      <c r="F11" s="38"/>
-      <c r="G11" s="38"/>
-      <c r="H11" s="37"/>
-      <c r="I11" s="38"/>
-      <c r="J11" s="38"/>
+      <c r="B10" s="30"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="C2:J2"/>
-    <mergeCell ref="A11:J11"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="C2:I2"/>
+    <mergeCell ref="A10:I10"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
   </mergeCells>
@@ -2121,144 +1974,144 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:T7"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="6"/>
+  <sheetFormatPr defaultColWidth="8.890625" defaultRowHeight="16.8" outlineLevelRow="6"/>
   <cols>
-    <col min="1" max="1" width="8.88888888888889" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="77.4444444444444" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="12.6666666666667" style="1" customWidth="1"/>
-    <col min="4" max="8" width="8.88888888888889" style="1"/>
-    <col min="9" max="9" width="11.4444444444444" style="1" customWidth="1"/>
-    <col min="10" max="14" width="8.88888888888889" style="1"/>
-    <col min="15" max="15" width="8.88888888888889" style="1" customWidth="1"/>
-    <col min="16" max="20" width="8.88888888888889" style="1"/>
+    <col min="1" max="1" width="8.890625" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="77.4453125" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" style="1" customWidth="1"/>
+    <col min="4" max="8" width="8.890625" style="1"/>
+    <col min="9" max="9" width="11.4453125" style="1" customWidth="1"/>
+    <col min="10" max="14" width="8.890625" style="1"/>
+    <col min="15" max="15" width="8.890625" style="1" customWidth="1"/>
+    <col min="16" max="20" width="8.890625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1" spans="1:20">
+    <row r="1" ht="25" customHeight="1" spans="3:20">
       <c r="C1" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
       <c r="K1" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
-      <c r="O1" s="3" t="s">
-        <v>53</v>
+      <c r="O1" s="11" t="s">
+        <v>48</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="Q1" s="2"/>
       <c r="R1" s="2"/>
       <c r="S1" s="2"/>
       <c r="T1" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" ht="34" customHeight="1" spans="3:20">
+      <c r="C2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="4"/>
+      <c r="E2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F2" s="4"/>
+      <c r="G2" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="H2" s="8"/>
+      <c r="I2" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="J2" s="10"/>
+      <c r="K2" s="3" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="2" ht="34" customHeight="1" spans="1:20">
-      <c r="C2" s="4" t="s">
+      <c r="L2" s="4"/>
+      <c r="M2" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D2" s="5"/>
-      <c r="E2" s="4" t="s">
+      <c r="N2" s="4"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="F2" s="5"/>
-      <c r="G2" s="6" t="s">
+      <c r="Q2" s="12"/>
+      <c r="R2" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="H2" s="7"/>
-      <c r="I2" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="J2" s="9"/>
-      <c r="K2" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="L2" s="5"/>
-      <c r="M2" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="N2" s="5"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q2" s="10"/>
-      <c r="R2" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="S2" s="5"/>
+      <c r="S2" s="4"/>
       <c r="T2" s="2"/>
     </row>
-    <row r="3" ht="21" customHeight="1" spans="1:20">
+    <row r="3" ht="21" customHeight="1" spans="3:20">
       <c r="C3" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="T3" s="2"/>
     </row>
     <row r="4" ht="71" customHeight="1" spans="1:20">
-      <c r="A4" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>66</v>
+      <c r="A4" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="C4" s="2">
         <v>2</v>
@@ -2325,12 +2178,12 @@
         <v>561</v>
       </c>
     </row>
-    <row r="5" ht="91" customHeight="1" spans="1:20">
-      <c r="A5" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>67</v>
+    <row r="5" ht="91" customHeight="1" spans="1:15">
+      <c r="A5" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>64</v>
       </c>
       <c r="C5" s="2">
         <v>2</v>
@@ -2379,12 +2232,12 @@
         <v>146</v>
       </c>
     </row>
-    <row r="6" ht="87" customHeight="1" spans="1:20">
-      <c r="A6" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>68</v>
+    <row r="6" ht="87" customHeight="1" spans="1:15">
+      <c r="A6" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>66</v>
       </c>
       <c r="C6" s="2">
         <v>2</v>
@@ -2433,12 +2286,12 @@
         <v>146</v>
       </c>
     </row>
-    <row r="7" ht="33" customHeight="1" spans="1:20">
+    <row r="7" ht="33" customHeight="1" spans="3:13">
       <c r="C7" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/notes/meetings/meeting-20260409/凤御美业八大会员权益.xlsx
+++ b/notes/meetings/meeting-20260409/凤御美业八大会员权益.xlsx
@@ -149,6 +149,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>定制明星美肤项目任选3次+</t>
     </r>
     <r>
@@ -414,10 +421,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="34">
     <font>
@@ -1133,19 +1140,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
